--- a/measurement/lagos_recording_manifest.xlsx
+++ b/measurement/lagos_recording_manifest.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lagos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="+0.0%;-0.0%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -49,12 +53,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -444,6 +450,46 @@
           <t>Correct Text</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Transcript (no keyterms)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Exact Match (no keyterms)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>WER (no keyterms)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Notes (no keyterms)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Transcript (with keyterms)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Exact Match (with keyterms)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>WER (with keyterms)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Notes (with keyterms)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -453,12 +499,48 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>los-01.m4a</t>
+          <t>los-01.aac</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>14 Adeniyi Jones Avenue, Ikeja</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>14 Adeniyi Jones Avenue Ikeja</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>14 Adeniyi Jones Avenue, Ikeja</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
         </is>
       </c>
     </row>
@@ -470,12 +552,48 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>los-02.m4a</t>
+          <t>los-02.aac</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Flat 3B, Parkview Estate, Ikoyi</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Flat 3B, Parkview Estate, Ikoyi.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Flat 3B, Parkview Estate, Ikoyi.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
         </is>
       </c>
     </row>
@@ -487,12 +605,48 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>los-03.m4a</t>
+          <t>los-03.aac</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>7 Osapa London, Lekki</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>7 Osapa London, Lekki.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>7 Osapa London, Lekki.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
         </is>
       </c>
     </row>
@@ -504,12 +658,48 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>los-04.m4a</t>
+          <t>los-04.aac</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>22 Opebi Road, Ikeja</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>22 Okpebi Road Ikeja</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>S=1, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22, Opebi Road, Ikeja</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
         </is>
       </c>
     </row>
@@ -521,12 +711,48 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>los-05.m4a</t>
+          <t>los-05.aac</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Block 4, Dolphin Estate, Ebute Metta</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Block 4, Dolphin Estate, Ebute Metta</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Block 4, Dolphin Estate, Ebute Metta</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
         </is>
       </c>
     </row>
@@ -538,12 +764,48 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>los-06.m4a</t>
+          <t>los-06.aac</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>9 Ogudu Road, Ojota</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>9 Ogudu Road, Ojota</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>9 Ogudu Road, Ojota.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
         </is>
       </c>
     </row>
@@ -555,12 +817,48 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>los-07.m4a</t>
+          <t>los-07.aac</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>18 Allen Avenue, Ikeja</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>18 Allen Avenue, Ikeja</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>18 Allen Avenue, Ikeja.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
         </is>
       </c>
     </row>
@@ -572,12 +870,48 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>los-08.m4a</t>
+          <t>los-08.aac</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>5 Awolowo Road, Ikoyi</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>5 Awolowo Road, Ikoyi</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>5 Awolowo Road, Ikoyi</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
         </is>
       </c>
     </row>
@@ -589,12 +923,48 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>los-09.m4a</t>
+          <t>los-09.aac</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>House 12, Ogba, near the roundabout</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>House 12, Ogba, near the roundabout</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>House 12, Ogba, near the roundabout.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
         </is>
       </c>
     </row>
@@ -606,12 +976,48 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>los-10.m4a</t>
+          <t>los-10.aac</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>31 Anthony Village, Gbagada</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>31 Anthony Village, Bagada</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>S=1, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>31 Anthony Village, Gbagada.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
         </is>
       </c>
     </row>
@@ -623,12 +1029,48 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>los-11.m4a</t>
+          <t>los-11.aac</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Flat 2, Lekki Phase One, Ikate</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Flat 2, Lekki Phase 1, Ikate</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>S=1, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Flat 2, Lekki Phase One, Ikate.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
         </is>
       </c>
     </row>
@@ -640,12 +1082,48 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>los-12.m4a</t>
+          <t>los-12.aac</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>9 Igbo Efon, off Chevron roundabout</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>9 Igboefo off Chevron roundabout</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>S=1, D=1, I=0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>9 Igbo Efon off Chevron roundabout</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
         </is>
       </c>
     </row>
@@ -657,12 +1135,48 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>los-13.m4a</t>
+          <t>los-13.aac</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>4 Oniru Estate, Victoria Island</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4 Oniru Estate, Victoria Island</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4, Oniru Estate, Victoria Island.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
         </is>
       </c>
     </row>
@@ -674,12 +1188,48 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>los-14.m4a</t>
+          <t>los-14.aac</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>27 Ketu, near the bus stop</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>27 Ketu near the bus stop</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>27 Ketu near the bus stop</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
         </is>
       </c>
     </row>
@@ -691,12 +1241,48 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>los-15.m4a</t>
+          <t>los-15.aac</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Shop 6, Festac, Amuwo Odofin</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Shop 6, Festac, Amuwo Odofin</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Shop 6, Festac, Amuwo Odofin.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
         </is>
       </c>
     </row>
@@ -708,12 +1294,48 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>los-16.m4a</t>
+          <t>los-16.aac</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>House 8, Magodo Phase Two</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>House 8, Magodo Phase 2</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>S=1, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>House 8, Magodo, Phase 2.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>S=1, D=0, I=0</t>
         </is>
       </c>
     </row>
@@ -725,12 +1347,48 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>los-17.m4a</t>
+          <t>los-17.aac</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>15 Surulere, close to Ojuelegba</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>15 Surulere Close to Ojuelegba</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>15 Surulere, close to Ojuelegba</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
         </is>
       </c>
     </row>
@@ -742,12 +1400,48 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>los-18.m4a</t>
+          <t>los-18.aac</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Block C, Banana Island, Ikoyi</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Block C, Banana Island, Ikoyi.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Block C, Banana Island, Ikoyi.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
         </is>
       </c>
     </row>
@@ -759,12 +1453,48 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>los-19.m4a</t>
+          <t>los-19.aac</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>44 Sangotedo, Ajah, after the filling station</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>44 Shongotedo Ajah after the filling station</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>S=1, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>44, Sangotedo, Ajah after the filling station</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
         </is>
       </c>
     </row>
@@ -776,12 +1506,174 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>los-20.m4a</t>
+          <t>los-20.aac</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>3 Elegushi Road, Lekki, by the gateman's post</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3 Elegushi Road, Lekki by the Gatesman Post</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>S=1, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>3, Elegushi Road, Lekki, by the Gatesman Post.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>S=1, D=0, I=0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>no keyterms</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>with keyterms</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Exact match</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Average WER</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0.073395</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0.01625</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>-0.057145</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Read this as</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Exact match should go up. WER should go down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Primary metric</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Normalized Exact Match</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Secondary diagnostic</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Word Error Rate (WER)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Clips scored</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Region pack</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ng-lagos (96 keyterms)</t>
         </is>
       </c>
     </row>
